--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -498,7 +498,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -530,7 +530,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -18,6 +18,103 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 无, 敌方, 我方, 自身</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>单体,横向,纵向,全部</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> All, 攻击,回复,复活,待机,增益,负面,移除负面</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>伤害=0,待机=1,治
+疗=2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
@@ -32,9 +129,6 @@
     <t>skillName</t>
   </si>
   <si>
-    <t>actionCount</t>
-  </si>
-  <si>
     <t>cd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -42,9 +136,6 @@
     <t>targetType</t>
   </si>
   <si>
-    <t>targetCount</t>
-  </si>
-  <si>
     <t>fightType</t>
   </si>
   <si>
@@ -80,13 +171,20 @@
   </si>
   <si>
     <t>角色攻击</t>
+  </si>
+  <si>
+    <t>actionValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>targetRangeType</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +205,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -417,11 +528,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:J5"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="12.875" style="1"/>
+    <col min="1" max="2" width="12.875" style="1"/>
+    <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="1"/>
+    <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
+    <col min="6" max="9" width="12.875" style="1"/>
     <col min="10" max="10" width="21" style="1" customWidth="1"/>
     <col min="11" max="16384" width="12.875" style="1"/>
   </cols>
@@ -431,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -466,28 +581,28 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -495,7 +610,7 @@
         <v>1001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>500</v>
@@ -504,13 +619,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -519,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -527,7 +642,7 @@
         <v>1002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>600</v>
@@ -536,13 +651,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -551,12 +666,13 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -32,6 +32,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> 无, 敌方, 我方, 自身</t>
@@ -41,6 +42,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,6 +58,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单体,横向,纵向,全部</t>
@@ -65,6 +68,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -80,6 +84,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> All, 攻击,回复,复活,待机,增益,负面,移除负面</t>
@@ -94,16 +99,17 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>伤害=0,待机=1,治
-疗=2</t>
+          <t>属性值, 固定值</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -116,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +184,16 @@
   </si>
   <si>
     <t>targetRangeType</t>
+  </si>
+  <si>
+    <t>iconName</t>
+  </si>
+  <si>
+    <t>寒冰斩</t>
+  </si>
+  <si>
+    <t>寒冰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -210,6 +226,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -217,6 +234,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -529,19 +547,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J5"/>
+  <dimension ref="A2:K6"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.875" style="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.875" style="1"/>
-    <col min="10" max="10" width="21" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.875" style="1"/>
+    <col min="6" max="10" width="12.875" style="1"/>
+    <col min="11" max="11" width="21" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,8 +590,11 @@
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -602,10 +623,13 @@
         <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1001</v>
       </c>
@@ -628,16 +652,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1002</v>
       </c>
@@ -660,13 +684,48 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>1100</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -701,7 +701,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -669,7 +669,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -701,7 +701,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -87,11 +87,85 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve"> All, 攻击,回复,复活,待机,增益,负面,移除负面</t>
+          <t>All, 攻击,回复,复活,待机,buff</t>
         </r>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>属性值, 固定值</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 无, 敌方, 我方, 自身</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>All, 攻击,回复,复活,待机,bu</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,9 +264,90 @@
   </si>
   <si>
     <t>寒冰斩</t>
-  </si>
-  <si>
-    <t>寒冰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒猎杀</t>
+  </si>
+  <si>
+    <t>烈焰斩</t>
+  </si>
+  <si>
+    <t>地刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+  </si>
+  <si>
+    <t>骑士冲击</t>
+  </si>
+  <si>
+    <t>血腥囚笼</t>
+  </si>
+  <si>
+    <t>龙卷风</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影突刺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧毒风暴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王之春</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>haveNextAction</t>
+  </si>
+  <si>
+    <t>holdTarget</t>
+  </si>
+  <si>
+    <t>nextTargetType</t>
+  </si>
+  <si>
+    <t>nextFightType</t>
+  </si>
+  <si>
+    <t>nextSkillActionType</t>
+  </si>
+  <si>
+    <t>nextActionValue</t>
+  </si>
+  <si>
+    <t>nextTimeLineDataName</t>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -200,7 +355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,13 +392,32 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -258,14 +432,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,89 +726,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K6"/>
+  <dimension ref="A2:R21"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.875" style="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
-    <col min="6" max="10" width="12.875" style="1"/>
-    <col min="11" max="11" width="21" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="12.875" style="1"/>
+    <col min="6" max="17" width="12.875" style="1"/>
+    <col min="18" max="18" width="21" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1001</v>
       </c>
@@ -654,14 +875,32 @@
       <c r="H4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1002</v>
       </c>
@@ -686,52 +925,883 @@
       <c r="H5" s="1">
         <v>100</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="I5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>1100</v>
+        <v>1009</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
+        <v>300</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
         <v>20</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>1100</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="C7" s="1">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>200</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>1191</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>200</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>1282</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>200</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>1373</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>150</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>1464</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>300</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>1555</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>200</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>1646</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>200</v>
+      </c>
+      <c r="I13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>1828</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>300</v>
+      </c>
+      <c r="I14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>1919</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>200</v>
+      </c>
+      <c r="I16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>2101</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>200</v>
+      </c>
+      <c r="I17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>2192</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>2283</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>300</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>2374</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>200</v>
+      </c>
+      <c r="I20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>2465</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>200</v>
+      </c>
+      <c r="I21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -151,7 +151,102 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>All, 攻击,回复,复活,待机,bu</t>
+          <t>All, 攻击</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>,回复</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>,复活</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>,待机</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>,bu</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>ff 5</t>
         </r>
         <r>
           <rPr>
@@ -196,7 +291,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -349,6 +444,73 @@
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标强力刺杀，目标额外受到固定伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率被冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率被点燃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成伤害，我方全部回复一定血量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成伤害，敌方有机率流血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率失明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体目标受到伤害</t>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率眩晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，幸运下降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率中毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，额外造成固定伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率降低防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标受到伤害后，有几率降低攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体目标受到伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -734,7 +896,7 @@
     <col min="4" max="4" width="12.875" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
     <col min="6" max="17" width="12.875" style="1"/>
-    <col min="18" max="18" width="21" style="1" customWidth="1"/>
+    <col min="18" max="18" width="27.5" style="1" customWidth="1"/>
     <col min="19" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
@@ -950,7 +1112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1009</v>
       </c>
@@ -976,22 +1138,22 @@
         <v>300</v>
       </c>
       <c r="I6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P6" s="1">
         <v>20</v>
@@ -1000,7 +1162,7 @@
         <v>20</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -1032,19 +1194,19 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>30</v>
@@ -1053,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -1085,19 +1247,19 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="1">
         <v>30</v>
@@ -1106,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1138,19 +1300,19 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P9" s="1">
         <v>30</v>
@@ -1159,10 +1321,10 @@
         <v>22</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>1373</v>
       </c>
@@ -1194,16 +1356,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P10" s="1">
         <v>50</v>
@@ -1212,10 +1374,10 @@
         <v>23</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>1464</v>
       </c>
@@ -1241,22 +1403,22 @@
         <v>300</v>
       </c>
       <c r="I11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" s="1">
         <v>20</v>
@@ -1265,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -1297,19 +1459,19 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" s="1">
         <v>30</v>
@@ -1318,7 +1480,7 @@
         <v>24</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -1347,10 +1509,10 @@
         <v>200</v>
       </c>
       <c r="I13" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -1371,7 +1533,7 @@
         <v>26</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -1403,19 +1565,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P14" s="1">
         <v>50</v>
@@ -1424,7 +1586,7 @@
         <v>27</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -1456,19 +1618,19 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P15" s="1">
         <v>30</v>
@@ -1476,8 +1638,8 @@
       <c r="Q15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="4" t="s">
-        <v>28</v>
+      <c r="R15" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1506,7 +1668,7 @@
         <v>200</v>
       </c>
       <c r="I16" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="b">
         <v>0</v>
@@ -1530,7 +1692,7 @@
         <v>29</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
@@ -1562,19 +1724,19 @@
         <v>1</v>
       </c>
       <c r="J17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P17" s="1">
         <v>50</v>
@@ -1583,7 +1745,7 @@
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -1636,7 +1798,7 @@
         <v>31</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -1644,7 +1806,7 @@
         <v>2283</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
@@ -1668,19 +1830,19 @@
         <v>1</v>
       </c>
       <c r="J19" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P19" s="1">
         <v>20</v>
@@ -1689,7 +1851,7 @@
         <v>32</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
@@ -1697,7 +1859,7 @@
         <v>2374</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
@@ -1721,19 +1883,19 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P20" s="1">
         <v>50</v>
@@ -1742,7 +1904,7 @@
         <v>33</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -1768,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I21" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>0</v>
@@ -1795,7 +1957,7 @@
         <v>34</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -291,7 +291,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -511,6 +511,43 @@
   <si>
     <t>刺颈鞭挞</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰斩</t>
+  </si>
+  <si>
+    <t>地刺</t>
+  </si>
+  <si>
+    <t>龙卷风</t>
+  </si>
+  <si>
+    <t>幻影突刺</t>
+  </si>
+  <si>
+    <t>剧毒风暴</t>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
+  </si>
+  <si>
+    <t>暴风雪</t>
+  </si>
+  <si>
+    <t>女王之春</t>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+  </si>
+  <si>
+    <t>雷暴</t>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -888,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:R21"/>
+  <dimension ref="A2:S21"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.875" style="1"/>
@@ -900,7 +937,7 @@
     <col min="19" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -955,8 +992,11 @@
       <c r="R2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1011,8 +1051,11 @@
       <c r="R3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="S3" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1001</v>
       </c>
@@ -1061,8 +1104,11 @@
       <c r="R4" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="S4" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1002</v>
       </c>
@@ -1111,8 +1157,11 @@
       <c r="R5" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="S5" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1009</v>
       </c>
@@ -1162,10 +1211,13 @@
         <v>20</v>
       </c>
       <c r="R6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>1100</v>
       </c>
@@ -1215,10 +1267,13 @@
         <v>19</v>
       </c>
       <c r="R7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>1191</v>
       </c>
@@ -1268,10 +1323,13 @@
         <v>21</v>
       </c>
       <c r="R8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1282</v>
       </c>
@@ -1321,10 +1379,13 @@
         <v>22</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>1373</v>
       </c>
@@ -1374,10 +1435,13 @@
         <v>23</v>
       </c>
       <c r="R10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>1464</v>
       </c>
@@ -1427,10 +1491,13 @@
         <v>25</v>
       </c>
       <c r="R11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>1555</v>
       </c>
@@ -1480,10 +1547,13 @@
         <v>24</v>
       </c>
       <c r="R12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>1646</v>
       </c>
@@ -1532,11 +1602,14 @@
       <c r="Q13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="R13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>1828</v>
       </c>
@@ -1585,11 +1658,14 @@
       <c r="Q14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>1919</v>
       </c>
@@ -1638,11 +1714,14 @@
       <c r="Q15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2010</v>
       </c>
@@ -1691,11 +1770,14 @@
       <c r="Q16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="R16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2101</v>
       </c>
@@ -1744,11 +1826,14 @@
       <c r="Q17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="R17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2192</v>
       </c>
@@ -1797,11 +1882,14 @@
       <c r="Q18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>2283</v>
       </c>
@@ -1850,11 +1938,14 @@
       <c r="Q19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="R19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>2374</v>
       </c>
@@ -1903,11 +1994,14 @@
       <c r="Q20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R20" s="3" t="s">
+      <c r="R20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>2465</v>
       </c>
@@ -1956,7 +2050,10 @@
       <c r="Q21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="R21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>50</v>
       </c>
     </row>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -61,7 +61,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>单体,横向,纵向,全部</t>
+          <t>单体,横向,纵向,全部,Null,Player</t>
         </r>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -547,6 +547,13 @@
   </si>
   <si>
     <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用道具</t>
+  </si>
+  <si>
+    <t>使用道具</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -925,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:S21"/>
+  <dimension ref="A2:S22"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.875" style="1"/>
@@ -1057,28 +1064,28 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="b">
         <v>0</v>
@@ -1102,18 +1109,18 @@
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1155,74 +1162,71 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>1009</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>300</v>
-      </c>
-      <c r="I6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>20</v>
-      </c>
-      <c r="P6" s="1">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>1100</v>
+        <v>1009</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
@@ -1231,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1240,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I7" s="1" t="b">
         <v>1</v>
@@ -1252,33 +1256,33 @@
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P7" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>1191</v>
+        <v>1100</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
         <v>8</v>
@@ -1314,27 +1318,27 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>30</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>1282</v>
+        <v>1191</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1370,27 +1374,27 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P9" s="1">
         <v>30</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>1373</v>
+        <v>1282</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>8</v>
@@ -1399,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1408,45 +1412,45 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P10" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>1464</v>
+        <v>1373</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -1455,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -1464,45 +1468,45 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P11" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>1555</v>
+        <v>1464</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>8</v>
@@ -1511,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -1520,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I12" s="1" t="b">
         <v>1</v>
@@ -1538,27 +1542,27 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>1555</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>1646</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1567,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -1579,7 +1583,7 @@
         <v>200</v>
       </c>
       <c r="I13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1" t="b">
         <v>1</v>
@@ -1588,33 +1592,33 @@
         <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P13" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>58</v>
+        <v>24</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>1828</v>
+        <v>1646</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
         <v>8</v>
@@ -1623,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1632,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I14" s="1" t="b">
         <v>0</v>
@@ -1644,33 +1648,33 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P14" s="1">
         <v>50</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>1919</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>28</v>
+        <v>1828</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="1">
         <v>8</v>
@@ -1679,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1688,10 +1692,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="b">
         <v>1</v>
@@ -1706,27 +1710,27 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P15" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>1919</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C16" s="1">
         <v>8</v>
@@ -1744,45 +1748,45 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I16" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P16" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1">
         <v>8</v>
@@ -1803,154 +1807,154 @@
         <v>200</v>
       </c>
       <c r="I17" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P17" s="1">
         <v>50</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2192</v>
+        <v>2101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1">
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I18" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P18" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2283</v>
+        <v>2192</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I19" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>2374</v>
+        <v>2283</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
@@ -1959,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -1968,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I20" s="1" t="b">
         <v>1</v>
@@ -1986,27 +1990,27 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2465</v>
+        <v>2374</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1">
         <v>8</v>
@@ -2024,36 +2028,92 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J21" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P21" s="1">
         <v>50</v>
       </c>
       <c r="Q21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>2465</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="C22" s="1">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>300</v>
+      </c>
+      <c r="I22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>50</v>
       </c>
     </row>

--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="SkillData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$F$7:$F$23</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -291,7 +295,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -505,7 +509,63 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>寒冰斩</t>
+  </si>
+  <si>
+    <t>地刺</t>
+  </si>
+  <si>
+    <t>龙卷风</t>
+  </si>
+  <si>
+    <t>幻影突刺</t>
+  </si>
+  <si>
+    <t>剧毒风暴</t>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
+  </si>
+  <si>
+    <t>暴风雪</t>
+  </si>
+  <si>
+    <t>女王之春</t>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+  </si>
+  <si>
     <t>雷暴</t>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用道具</t>
+  </si>
+  <si>
+    <t>使用道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士冲击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -513,47 +573,35 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>诅咒猎杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>寒冰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>地刺</t>
-  </si>
-  <si>
-    <t>龙卷风</t>
-  </si>
-  <si>
-    <t>幻影突刺</t>
-  </si>
-  <si>
-    <t>剧毒风暴</t>
-  </si>
-  <si>
-    <t>恶魔幻影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥囚笼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>暴风雪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>女王之春</t>
-  </si>
-  <si>
-    <t>刺颈鞭挞</t>
-  </si>
-  <si>
-    <t>雷暴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>幽冥黑洞</t>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用道具</t>
-  </si>
-  <si>
-    <t>使用道具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yyy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1059,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -1067,7 +1115,7 @@
         <v>1000</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1109,10 +1157,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -1226,7 +1274,7 @@
         <v>1009</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
@@ -1282,7 +1330,7 @@
         <v>1100</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C8" s="1">
         <v>8</v>
@@ -1327,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>45</v>
@@ -1338,7 +1386,7 @@
         <v>1191</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1394,7 +1442,7 @@
         <v>1282</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1">
         <v>8</v>
@@ -1439,7 +1487,7 @@
         <v>22</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>49</v>
@@ -1450,7 +1498,7 @@
         <v>1373</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -1506,7 +1554,7 @@
         <v>1464</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C12" s="1">
         <v>8</v>
@@ -1562,7 +1610,7 @@
         <v>1555</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1663,7 +1711,7 @@
         <v>26</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>58</v>
@@ -1719,7 +1767,7 @@
         <v>27</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>52</v>
@@ -1775,7 +1823,7 @@
         <v>28</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>53</v>
@@ -1786,7 +1834,7 @@
         <v>2010</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1">
         <v>8</v>
@@ -1831,7 +1879,7 @@
         <v>29</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>50</v>
@@ -1842,7 +1890,7 @@
         <v>2101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1">
         <v>8</v>
@@ -1851,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -1887,7 +1935,7 @@
         <v>30</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>54</v>
@@ -1898,7 +1946,7 @@
         <v>2192</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
@@ -1943,7 +1991,7 @@
         <v>31</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>55</v>
@@ -1954,7 +2002,7 @@
         <v>2283</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
@@ -1963,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -1999,7 +2047,7 @@
         <v>32</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>56</v>
@@ -2010,7 +2058,7 @@
         <v>2374</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <v>8</v>
@@ -2019,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -2055,7 +2103,7 @@
         <v>33</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>57</v>
@@ -2066,7 +2114,7 @@
         <v>2465</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C22" s="1">
         <v>8</v>
@@ -2111,7 +2159,7 @@
         <v>34</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>50</v>
@@ -2123,4 +2171,117 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="F7:H23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="7" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="F7:F23">
+    <sortState ref="F8:F23">
+      <sortCondition ref="F7:F23"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/SkillData.xlsx
+++ b/Datas/SkillData.xlsx
@@ -129,6 +129,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> 无, 敌方, 我方, 自身</t>
@@ -138,6 +139,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -153,6 +155,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>All, 攻击</t>
@@ -174,6 +177,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>,回复</t>
@@ -195,6 +199,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>,复活</t>
@@ -216,6 +221,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>,待机</t>
@@ -237,6 +243,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>,bu</t>
@@ -257,6 +264,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -295,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -603,13 +611,30 @@
   <si>
     <t>yyy</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用回血道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用回蓝道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用回血蓝道具</t>
+  </si>
+  <si>
+    <t>使用回体力道具</t>
+  </si>
+  <si>
+    <t>使用回血蓝力道具</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -646,19 +671,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -686,7 +698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -699,6 +711,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -980,16 +995,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:S22"/>
+  <dimension ref="A2:S27"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.875" style="1"/>
+    <col min="1" max="1" width="12.875" style="1"/>
+    <col min="2" max="2" width="17.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
     <col min="6" max="17" width="12.875" style="1"/>
     <col min="18" max="18" width="27.5" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="12.875" style="1"/>
+    <col min="19" max="19" width="18.5" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -1112,10 +1129,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1157,36 +1174,36 @@
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="b">
         <v>0</v>
@@ -1210,351 +1227,336 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
+        <v>902</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>903</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>904</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>1002</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1" t="s">
+      <c r="I11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="12" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>1009</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>300</v>
-      </c>
-      <c r="I7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>20</v>
-      </c>
-      <c r="P7" s="1">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>1100</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="1">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>200</v>
-      </c>
-      <c r="I8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>5</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>1191</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>200</v>
-      </c>
-      <c r="I9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>5</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>1282</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="1">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>200</v>
-      </c>
-      <c r="I10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>5</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>1373</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>150</v>
-      </c>
-      <c r="I11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>10</v>
-      </c>
-      <c r="P11" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>1464</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C12" s="1">
         <v>8</v>
@@ -1584,33 +1586,33 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="P12" s="1">
         <v>20</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>1555</v>
+        <v>1100</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1646,27 +1648,27 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1">
         <v>30</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>1646</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>1191</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="1">
         <v>8</v>
@@ -1675,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1687,7 +1689,7 @@
         <v>200</v>
       </c>
       <c r="I14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1" t="b">
         <v>1</v>
@@ -1696,33 +1698,33 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>1828</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>1282</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C15" s="1">
         <v>8</v>
@@ -1731,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1740,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1" t="b">
         <v>1</v>
@@ -1758,27 +1760,27 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P15" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>1919</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>1373</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C16" s="1">
         <v>8</v>
@@ -1796,45 +1798,45 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J16" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P16" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>1464</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C17" s="1">
         <v>8</v>
@@ -1843,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -1852,45 +1854,45 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2101</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>82</v>
+        <v>1555</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C18" s="1">
         <v>8</v>
@@ -1899,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -1920,57 +1922,57 @@
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1">
+        <v>3</v>
+      </c>
+      <c r="P18" s="1">
         <v>30</v>
       </c>
-      <c r="P18" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>30</v>
+      <c r="Q18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2192</v>
+        <v>1646</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J19" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -1985,24 +1987,24 @@
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>2283</v>
+        <v>1828</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
@@ -2011,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -2023,7 +2025,7 @@
         <v>300</v>
       </c>
       <c r="I20" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1" t="b">
         <v>1</v>
@@ -2038,27 +2040,27 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P20" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2374</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>1919</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="1">
         <v>8</v>
@@ -2067,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -2076,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I21" s="1" t="b">
         <v>1</v>
@@ -2094,27 +2096,27 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P21" s="1">
-        <v>50</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2465</v>
+        <v>2010</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1">
         <v>8</v>
@@ -2132,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I22" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>0</v>
@@ -2156,12 +2158,292 @@
         <v>50</v>
       </c>
       <c r="Q22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>2101</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="1">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>200</v>
+      </c>
+      <c r="I23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1">
+        <v>30</v>
+      </c>
+      <c r="P23" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>2192</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="1">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>2283</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="1">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>300</v>
+      </c>
+      <c r="I25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>7</v>
+      </c>
+      <c r="P25" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>2374</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>200</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>8</v>
+      </c>
+      <c r="P26" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>2465</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="1">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>300</v>
+      </c>
+      <c r="I27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S27" s="5" t="s">
         <v>50</v>
       </c>
     </row>
